--- a/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R85-RolePriseCharge.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R85-RolePriseCharge.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
